--- a/Used_Cars_Spends.xlsx
+++ b/Used_Cars_Spends.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\used_cars_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E942D63-8855-4EC4-A6B0-5C2BDAD6F472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{958797C1-4099-48EA-A561-A2B6F0238B4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{AB0BC2DF-AFB8-4F7F-8E7C-C5CCB010599F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{AB0BC2DF-AFB8-4F7F-8E7C-C5CCB010599F}"/>
   </bookViews>
   <sheets>
     <sheet name="Ga" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="14">
   <si>
     <t>Day</t>
   </si>
@@ -79,6 +79,12 @@
   </si>
   <si>
     <t>Nasik-Search-Buy-UsedCar-8april</t>
+  </si>
+  <si>
+    <t>Nashik-DSA-UsedCars-Discovery</t>
+  </si>
+  <si>
+    <t>UCR-Lead-Luxury-Cart-Classified-Jan25</t>
   </si>
 </sst>
 </file>
@@ -452,9 +458,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C4A3642-CB73-4C6E-982D-175B4617F108}">
-  <dimension ref="A1:C211"/>
+  <dimension ref="A1:C218"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2777,6 +2784,83 @@
       </c>
       <c r="C211">
         <v>1002.08</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A212" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B212" t="s">
+        <v>12</v>
+      </c>
+      <c r="C212">
+        <v>298.89</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A213" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B213" t="s">
+        <v>11</v>
+      </c>
+      <c r="C213">
+        <v>2818.5</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A214" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B214" t="s">
+        <v>11</v>
+      </c>
+      <c r="C214">
+        <v>1690.68</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A215" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B215" t="s">
+        <v>4</v>
+      </c>
+      <c r="C215">
+        <v>997.2</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A216" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B216" t="s">
+        <v>4</v>
+      </c>
+      <c r="C216">
+        <v>822.2</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A217" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B217" t="s">
+        <v>5</v>
+      </c>
+      <c r="C217">
+        <v>1100.55</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A218" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B218" t="s">
+        <v>5</v>
+      </c>
+      <c r="C218">
+        <v>1007.25</v>
       </c>
     </row>
   </sheetData>
@@ -2787,7 +2871,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83E96F97-1063-4144-86B8-47E4992E248F}">
-  <dimension ref="A1:C211"/>
+  <dimension ref="A1:C219"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.7265625" bestFit="1" customWidth="1"/>
@@ -5116,6 +5200,94 @@
         <v>512.59</v>
       </c>
     </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A212" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B212" t="s">
+        <v>9</v>
+      </c>
+      <c r="C212">
+        <v>505.51</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A213" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B213" t="s">
+        <v>3</v>
+      </c>
+      <c r="C213">
+        <v>3168.19</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A214" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B214" t="s">
+        <v>10</v>
+      </c>
+      <c r="C214">
+        <v>505.17</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A215" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B215" t="s">
+        <v>13</v>
+      </c>
+      <c r="C215">
+        <v>581.89</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A216" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B216" t="s">
+        <v>9</v>
+      </c>
+      <c r="C216">
+        <v>458.08</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A217" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B217" t="s">
+        <v>3</v>
+      </c>
+      <c r="C217">
+        <v>2587.6</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A218" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B218" t="s">
+        <v>10</v>
+      </c>
+      <c r="C218">
+        <v>493.44</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A219" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B219" t="s">
+        <v>13</v>
+      </c>
+      <c r="C219">
+        <v>393.54</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Used_Cars_Spends.xlsx
+++ b/Used_Cars_Spends.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepanshi Ahuja\Desktop\used_cars_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{958797C1-4099-48EA-A561-A2B6F0238B4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D4F6B12-BD27-4E9D-8A83-7CF4B86196E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{AB0BC2DF-AFB8-4F7F-8E7C-C5CCB010599F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{AB0BC2DF-AFB8-4F7F-8E7C-C5CCB010599F}"/>
   </bookViews>
   <sheets>
     <sheet name="Ga" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="12">
   <si>
     <t>Day</t>
   </si>
@@ -79,12 +79,6 @@
   </si>
   <si>
     <t>Nasik-Search-Buy-UsedCar-8april</t>
-  </si>
-  <si>
-    <t>Nashik-DSA-UsedCars-Discovery</t>
-  </si>
-  <si>
-    <t>UCR-Lead-Luxury-Cart-Classified-Jan25</t>
   </si>
 </sst>
 </file>
@@ -458,7 +452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C4A3642-CB73-4C6E-982D-175B4617F108}">
-  <dimension ref="A1:C218"/>
+  <dimension ref="A1:C217"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
@@ -2791,75 +2785,64 @@
         <v>46183</v>
       </c>
       <c r="B212" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C212">
-        <v>298.89</v>
+        <v>2818.5</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A213" s="1">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B213" t="s">
         <v>11</v>
       </c>
       <c r="C213">
-        <v>2818.5</v>
+        <v>1690.68</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A214" s="1">
-        <v>46184</v>
+        <v>46183</v>
       </c>
       <c r="B214" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C214">
-        <v>1690.68</v>
+        <v>997.2</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A215" s="1">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B215" t="s">
         <v>4</v>
       </c>
       <c r="C215">
-        <v>997.2</v>
+        <v>822.2</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A216" s="1">
-        <v>46184</v>
+        <v>46183</v>
       </c>
       <c r="B216" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C216">
-        <v>822.2</v>
+        <v>1100.55</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A217" s="1">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B217" t="s">
         <v>5</v>
       </c>
       <c r="C217">
-        <v>1100.55</v>
-      </c>
-    </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A218" s="1">
-        <v>46184</v>
-      </c>
-      <c r="B218" t="s">
-        <v>5</v>
-      </c>
-      <c r="C218">
         <v>1007.25</v>
       </c>
     </row>
@@ -2871,7 +2854,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83E96F97-1063-4144-86B8-47E4992E248F}">
-  <dimension ref="A1:C219"/>
+  <dimension ref="A1:C217"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.7265625" bestFit="1" customWidth="1"/>
@@ -5235,13 +5218,13 @@
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A215" s="1">
-        <v>46184</v>
+        <v>46183</v>
       </c>
       <c r="B215" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C215">
-        <v>581.89</v>
+        <v>458.08</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.35">
@@ -5249,10 +5232,10 @@
         <v>46183</v>
       </c>
       <c r="B216" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C216">
-        <v>458.08</v>
+        <v>2587.6</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.35">
@@ -5260,32 +5243,10 @@
         <v>46183</v>
       </c>
       <c r="B217" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C217">
-        <v>2587.6</v>
-      </c>
-    </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A218" s="1">
-        <v>46183</v>
-      </c>
-      <c r="B218" t="s">
-        <v>10</v>
-      </c>
-      <c r="C218">
         <v>493.44</v>
-      </c>
-    </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A219" s="1">
-        <v>46183</v>
-      </c>
-      <c r="B219" t="s">
-        <v>13</v>
-      </c>
-      <c r="C219">
-        <v>393.54</v>
       </c>
     </row>
   </sheetData>
